--- a/data/file_generation/input/data_67/A文件-物流公司费用数据分析.xlsx
+++ b/data/file_generation/input/data_67/A文件-物流公司费用数据分析.xlsx
@@ -1901,26 +1901,18 @@
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="eca6eae4-1627-4e8d-9a6b-5b4dd91506e7">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-  </documentManagement>
+  <documentManagement/>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81DBED13-10BF-4EB5-B937-BFC95C0911F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE9B9C4D-8FD4-4F08-9E1F-307B3F63639A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E3E6964-D8F3-4A13-B9DF-B847EEDEB49F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B91CBBC4-F718-4EB7-A4DC-AAF044F9E380}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{93866D75-D1A1-403D-A705-5F7A3F182FE6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F7DF077-6E27-469D-8CCB-83A1FFBA16E4}"/>
 </file>